--- a/research/traditional_assets/database/data/macedonia/macedonia_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/macedonia/macedonia_metals_mining.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-5.35</v>
+        <v>-6.25</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.108</v>
+        <v>0.06</v>
       </c>
       <c r="V2">
-        <v>0.006033519553072626</v>
+        <v>0.002553191489361702</v>
       </c>
       <c r="W2">
-        <v>-1.16557734204793</v>
+        <v>10</v>
       </c>
       <c r="X2">
-        <v>0.1616425175448321</v>
+        <v>0.2750090808176291</v>
       </c>
       <c r="Y2">
-        <v>-1.327219859592762</v>
+        <v>9.724990919182371</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.1824618736383442</v>
+        <v>-0.07328104425488063</v>
       </c>
       <c r="AB2">
-        <v>0.1361829689109889</v>
+        <v>0.1920230721203851</v>
       </c>
       <c r="AC2">
-        <v>-0.3186448425493331</v>
+        <v>-0.2653041163752657</v>
       </c>
       <c r="AD2">
-        <v>18.2</v>
+        <v>19.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18.2</v>
+        <v>19.6</v>
       </c>
       <c r="AG2">
-        <v>18.092</v>
+        <v>19.54</v>
       </c>
       <c r="AH2">
-        <v>0.5041551246537397</v>
+        <v>0.4547563805104409</v>
       </c>
       <c r="AI2">
-        <v>1.035561877667141</v>
+        <v>1.513513513513514</v>
       </c>
       <c r="AJ2">
-        <v>0.5026672593909758</v>
+        <v>0.453996282527881</v>
       </c>
       <c r="AK2">
-        <v>1.035781759890078</v>
+        <v>1.515903801396431</v>
       </c>
       <c r="AL2">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AM2">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AN2">
-        <v>-5.449101796407185</v>
+        <v>-15.3125</v>
       </c>
       <c r="AO2">
-        <v>-1.580188679245283</v>
+        <v>-0.5898617511520737</v>
       </c>
       <c r="AP2">
-        <v>-5.416766467065868</v>
+        <v>-15.265625</v>
       </c>
       <c r="AQ2">
-        <v>-1.580188679245283</v>
+        <v>-0.5898617511520737</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-5.35</v>
+        <v>-6.25</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.108</v>
+        <v>0.06</v>
       </c>
       <c r="V3">
-        <v>0.006033519553072626</v>
+        <v>0.002553191489361702</v>
       </c>
       <c r="W3">
-        <v>-1.16557734204793</v>
+        <v>10</v>
       </c>
       <c r="X3">
-        <v>0.1616425175448321</v>
+        <v>0.2750090808176291</v>
       </c>
       <c r="Y3">
-        <v>-1.327219859592762</v>
+        <v>9.724990919182371</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.1824618736383442</v>
+        <v>-0.07328104425488063</v>
       </c>
       <c r="AB3">
-        <v>0.1361829689109889</v>
+        <v>0.1920230721203851</v>
       </c>
       <c r="AC3">
-        <v>-0.3186448425493331</v>
+        <v>-0.2653041163752657</v>
       </c>
       <c r="AD3">
-        <v>18.2</v>
+        <v>19.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.2</v>
+        <v>19.6</v>
       </c>
       <c r="AG3">
-        <v>18.092</v>
+        <v>19.54</v>
       </c>
       <c r="AH3">
-        <v>0.5041551246537397</v>
+        <v>0.4547563805104409</v>
       </c>
       <c r="AI3">
-        <v>1.035561877667141</v>
+        <v>1.513513513513514</v>
       </c>
       <c r="AJ3">
-        <v>0.5026672593909758</v>
+        <v>0.453996282527881</v>
       </c>
       <c r="AK3">
-        <v>1.035781759890078</v>
+        <v>1.515903801396431</v>
       </c>
       <c r="AL3">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AM3">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AN3">
-        <v>-5.449101796407185</v>
+        <v>-15.3125</v>
       </c>
       <c r="AO3">
-        <v>-1.580188679245283</v>
+        <v>-0.5898617511520737</v>
       </c>
       <c r="AP3">
-        <v>-5.416766467065868</v>
+        <v>-15.265625</v>
       </c>
       <c r="AQ3">
-        <v>-1.580188679245283</v>
+        <v>-0.5898617511520737</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/macedonia/macedonia_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/macedonia/macedonia_metals_mining.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-6.25</v>
+        <v>-3.79</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.06</v>
+        <v>1.07</v>
       </c>
       <c r="V2">
-        <v>0.002553191489361702</v>
+        <v>0.08230769230769232</v>
       </c>
       <c r="W2">
-        <v>10</v>
+        <v>0.5699248120300752</v>
       </c>
       <c r="X2">
-        <v>0.2750090808176291</v>
+        <v>0.2708823617849131</v>
       </c>
       <c r="Y2">
-        <v>9.724990919182371</v>
+        <v>0.2990424502451621</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.07328104425488063</v>
+        <v>-0.2117920868890613</v>
       </c>
       <c r="AB2">
-        <v>0.1920230721203851</v>
+        <v>0.1570548722963887</v>
       </c>
       <c r="AC2">
-        <v>-0.2653041163752657</v>
+        <v>-0.36884695918545</v>
       </c>
       <c r="AD2">
-        <v>19.6</v>
+        <v>20.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>19.6</v>
+        <v>20.1</v>
       </c>
       <c r="AG2">
-        <v>19.54</v>
+        <v>19.03</v>
       </c>
       <c r="AH2">
-        <v>0.4547563805104409</v>
+        <v>0.6072507552870091</v>
       </c>
       <c r="AI2">
-        <v>1.513513513513514</v>
+        <v>1.28352490421456</v>
       </c>
       <c r="AJ2">
-        <v>0.453996282527881</v>
+        <v>0.5941305026537621</v>
       </c>
       <c r="AK2">
-        <v>1.515903801396431</v>
+        <v>1.304318026045237</v>
       </c>
       <c r="AL2">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="AM2">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="AN2">
-        <v>-15.3125</v>
+        <v>-7.362637362637363</v>
       </c>
       <c r="AO2">
-        <v>-0.5898617511520737</v>
+        <v>-1.151898734177215</v>
       </c>
       <c r="AP2">
-        <v>-15.265625</v>
+        <v>-6.970695970695971</v>
       </c>
       <c r="AQ2">
-        <v>-0.5898617511520737</v>
+        <v>-1.151898734177215</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-6.25</v>
+        <v>-3.79</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.06</v>
+        <v>1.07</v>
       </c>
       <c r="V3">
-        <v>0.002553191489361702</v>
+        <v>0.08230769230769232</v>
       </c>
       <c r="W3">
-        <v>10</v>
+        <v>0.5699248120300752</v>
       </c>
       <c r="X3">
-        <v>0.2750090808176291</v>
+        <v>0.2708823617849131</v>
       </c>
       <c r="Y3">
-        <v>9.724990919182371</v>
+        <v>0.2990424502451621</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.07328104425488063</v>
+        <v>-0.2117920868890613</v>
       </c>
       <c r="AB3">
-        <v>0.1920230721203851</v>
+        <v>0.1570548722963887</v>
       </c>
       <c r="AC3">
-        <v>-0.2653041163752657</v>
+        <v>-0.36884695918545</v>
       </c>
       <c r="AD3">
-        <v>19.6</v>
+        <v>20.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>19.6</v>
+        <v>20.1</v>
       </c>
       <c r="AG3">
-        <v>19.54</v>
+        <v>19.03</v>
       </c>
       <c r="AH3">
-        <v>0.4547563805104409</v>
+        <v>0.6072507552870091</v>
       </c>
       <c r="AI3">
-        <v>1.513513513513514</v>
+        <v>1.28352490421456</v>
       </c>
       <c r="AJ3">
-        <v>0.453996282527881</v>
+        <v>0.5941305026537621</v>
       </c>
       <c r="AK3">
-        <v>1.515903801396431</v>
+        <v>1.304318026045237</v>
       </c>
       <c r="AL3">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="AM3">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="AN3">
-        <v>-15.3125</v>
+        <v>-7.362637362637363</v>
       </c>
       <c r="AO3">
-        <v>-0.5898617511520737</v>
+        <v>-1.151898734177215</v>
       </c>
       <c r="AP3">
-        <v>-15.265625</v>
+        <v>-6.970695970695971</v>
       </c>
       <c r="AQ3">
-        <v>-0.5898617511520737</v>
+        <v>-1.151898734177215</v>
       </c>
     </row>
   </sheetData>
